--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487399_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487399_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7579</v>
+        <v>9.043799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.905099999999999</v>
+        <v>6.9772</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8527</v>
+        <v>2.0666</v>
       </c>
       <c r="G2" t="n">
         <v>3.2249</v>
@@ -610,13 +610,13 @@
         <v>0.9792</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3548</v>
+        <v>2.6407</v>
       </c>
       <c r="T2" t="n">
-        <v>4.2169</v>
+        <v>2.289</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1379</v>
+        <v>0.3517</v>
       </c>
       <c r="V2" t="n">
         <v>2.1989</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. HERNANDEZ GARCIA</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5776</v>
+        <v>6.5689</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3628</v>
+        <v>6.0809</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2148</v>
+        <v>0.488</v>
       </c>
       <c r="G3" t="n">
-        <v>4.592</v>
+        <v>6.8682</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1626</v>
+        <v>5.655</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4294</v>
+        <v>1.2132</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4869</v>
+        <v>6.0923</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1595</v>
+        <v>5.4456</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6726</v>
+        <v>0.6466</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1051</v>
+        <v>0.7759</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0031</v>
+        <v>0.2094</v>
       </c>
       <c r="O3" t="n">
-        <v>1.102</v>
+        <v>0.5666</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.7419</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S3" t="n">
-        <v>5.3524</v>
+        <v>0.9143</v>
       </c>
       <c r="T3" t="n">
-        <v>4.6327</v>
+        <v>0.7881</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7196</v>
+        <v>0.1262</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6248</v>
+        <v>-0.2343</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1602</v>
+        <v>1.159</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.785</v>
+        <v>-1.3933</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>S. GONZALEZ MOTA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1211</v>
+        <v>6.1901</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7935</v>
+        <v>4.9637</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3276</v>
+        <v>1.2264</v>
       </c>
       <c r="G4" t="n">
-        <v>6.8682</v>
+        <v>4.6349</v>
       </c>
       <c r="H4" t="n">
-        <v>5.655</v>
+        <v>1.128</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2132</v>
+        <v>3.5068</v>
       </c>
       <c r="J4" t="n">
-        <v>6.0923</v>
+        <v>4.5246</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4456</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6466</v>
+        <v>3.8798</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7759</v>
+        <v>0.1103</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2094</v>
+        <v>0.4833</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5666</v>
+        <v>-0.373</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9792</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5336</v>
+        <v>1.2988</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4993</v>
+        <v>1.181</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0342</v>
+        <v>0.1178</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2343</v>
+        <v>1.0399</v>
       </c>
       <c r="W4" t="n">
-        <v>1.159</v>
+        <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3933</v>
+        <v>-0.1767</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. GONZALEZ MOTA</t>
+          <t>S. HERNANDEZ GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.4652</v>
+        <v>4.2312</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1052</v>
+        <v>2.2302</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3601</v>
+        <v>2.0009</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6349</v>
+        <v>4.592</v>
       </c>
       <c r="H5" t="n">
-        <v>1.128</v>
+        <v>4.1626</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5068</v>
+        <v>0.4294</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5246</v>
+        <v>3.4869</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6447000000000001</v>
+        <v>4.1595</v>
       </c>
       <c r="L5" t="n">
-        <v>3.8798</v>
+        <v>-0.6726</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1103</v>
+        <v>1.1051</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4833</v>
+        <v>0.0031</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.373</v>
+        <v>1.102</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7834</v>
+        <v>-2.7419</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R5" t="n">
         <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4261</v>
+        <v>3.006</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6775</v>
+        <v>2.5002</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2514</v>
+        <v>0.5058</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0399</v>
+        <v>-0.6248</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2166</v>
+        <v>0.1602</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1767</v>
+        <v>-0.785</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8023</v>
+        <v>2.8127</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1581</v>
+        <v>3.8744</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3557</v>
+        <v>-1.0617</v>
       </c>
       <c r="G6" t="n">
         <v>2.4296</v>
@@ -922,13 +922,13 @@
         <v>0.9792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5697</v>
+        <v>0.4407</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0288</v>
+        <v>0.7452</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5985</v>
+        <v>-0.3045</v>
       </c>
       <c r="V6" t="n">
         <v>-0.0576</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3925</v>
+        <v>2.0276</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5495</v>
+        <v>-0.0213</v>
       </c>
       <c r="F7" t="n">
-        <v>1.942</v>
+        <v>2.0489</v>
       </c>
       <c r="G7" t="n">
         <v>3.3907</v>
@@ -1000,13 +1000,13 @@
         <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2142</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5328000000000001</v>
+        <v>1.061</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3186</v>
+        <v>-0.2117</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2331</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. PETERS</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8327</v>
+        <v>0.9296</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3224</v>
+        <v>3.2594</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5103</v>
+        <v>-2.3298</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7147</v>
+        <v>1.8905</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.589</v>
+        <v>0.2535</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1257</v>
+        <v>1.637</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4032</v>
+        <v>3.0083</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5245</v>
+        <v>0.4525</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1212</v>
+        <v>2.5558</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3115</v>
+        <v>-1.1177</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0646</v>
+        <v>-0.199</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2469</v>
+        <v>-0.9188</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>1.923</v>
+        <v>-0.3319</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7256</v>
+        <v>0.2511</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1974</v>
+        <v>-0.583</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5507</v>
+        <v>-1.2166</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5507</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>R. PETERS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.073</v>
+        <v>0.027</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1766</v>
+        <v>-0.1893</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2496</v>
+        <v>0.2163</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8905</v>
+        <v>-1.7147</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2535</v>
+        <v>-1.589</v>
       </c>
       <c r="I9" t="n">
-        <v>1.637</v>
+        <v>-0.1257</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0083</v>
+        <v>-1.4032</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4525</v>
+        <v>-1.5245</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5558</v>
+        <v>0.1212</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1177</v>
+        <v>-0.3115</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.199</v>
+        <v>-0.0646</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9188</v>
+        <v>-0.2469</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3344</v>
+        <v>1.1173</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8316</v>
+        <v>1.2139</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5028</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2166</v>
+        <v>-0.5507</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2166</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="10">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6499</v>
+        <v>-0.5522</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5706</v>
+        <v>-1.3659</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9207</v>
+        <v>0.8137</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1517</v>
@@ -1312,13 +1312,13 @@
         <v>0.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0893</v>
+        <v>0.187</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.297</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3863</v>
+        <v>0.2794</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9017</v>
+        <v>-2.3599</v>
       </c>
       <c r="E13" t="n">
-        <v>0.277</v>
+        <v>-0.2347</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1786</v>
+        <v>-2.1252</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8924</v>
@@ -1468,13 +1468,13 @@
         <v>0.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.3367</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0081</v>
+        <v>0.4964</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2131</v>
+        <v>-0.1597</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2166</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>26.5598</v>
+        <v>27.1539</v>
       </c>
       <c r="E14" t="n">
-        <v>24.9806</v>
+        <v>25.5746</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5794</v>
+        <v>1.579199999999999</v>
       </c>
       <c r="G14" t="n">
         <v>24.5449</v>
@@ -1516,16 +1516,16 @@
         <v>14.9676</v>
       </c>
       <c r="I14" t="n">
-        <v>9.577300000000003</v>
+        <v>9.577300000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>22.24910000000001</v>
+        <v>22.2491</v>
       </c>
       <c r="K14" t="n">
         <v>14.2437</v>
       </c>
       <c r="L14" t="n">
-        <v>8.005099999999999</v>
+        <v>8.005100000000001</v>
       </c>
       <c r="M14" t="n">
         <v>2.2961</v>
@@ -1546,13 +1546,13 @@
         <v>8.813000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>9.319100000000001</v>
+        <v>9.9132</v>
       </c>
       <c r="T14" t="n">
-        <v>9.839499999999999</v>
+        <v>10.4336</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5203000000000002</v>
+        <v>-0.5202999999999998</v>
       </c>
       <c r="V14" t="n">
         <v>-3.3869</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0729</v>
+        <v>6.5034</v>
       </c>
       <c r="E15" t="n">
         <v>9.590999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5181</v>
+        <v>-3.0876</v>
       </c>
       <c r="G15" t="n">
         <v>2.65</v>
@@ -1624,13 +1624,13 @@
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0691</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="T15" t="n">
         <v>0.4493</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.5184</v>
+        <v>-1.0879</v>
       </c>
       <c r="V15" t="n">
         <v>3.3169</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1981</v>
+        <v>3.1578</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6283</v>
+        <v>5.3446</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4302</v>
+        <v>-2.1868</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1152</v>
@@ -1702,13 +1702,13 @@
         <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.2789</v>
+        <v>-1.3192</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0933</v>
+        <v>-0.377</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1856</v>
+        <v>-0.9422</v>
       </c>
       <c r="V16" t="n">
         <v>4.2005</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. CAAMAÑO ARAGUNDE</t>
+          <t>P. SERQUEIRA ALVAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5671</v>
+        <v>-0.1534</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.879</v>
+        <v>-0.4497</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3119</v>
+        <v>0.2963</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1122</v>
+        <v>-0.7558</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0258</v>
+        <v>-0.2504</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0864</v>
+        <v>-0.5054</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6414</v>
+        <v>-0.6214</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0408</v>
+        <v>0.0204</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6822</v>
+        <v>-0.6418</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4708</v>
+        <v>-0.1344</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0667</v>
+        <v>-0.2708</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4042</v>
+        <v>0.1364</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0412</v>
+        <v>-0.181</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2376</v>
+        <v>0.1717</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1964</v>
+        <v>-0.3527</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3905</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. SERQUEIRA ALVAREZ</t>
+          <t>C. CAAMAÑO ARAGUNDE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6429</v>
+        <v>-0.7542</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.859</v>
+        <v>-0.879</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2161</v>
+        <v>0.1248</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7558</v>
+        <v>-1.1122</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2504</v>
+        <v>-0.0258</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5054</v>
+        <v>-1.0864</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6214</v>
+        <v>-0.6414</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0204</v>
+        <v>0.0408</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6418</v>
+        <v>-0.6822</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1344</v>
+        <v>-0.4708</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2708</v>
+        <v>-0.0667</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1364</v>
+        <v>-0.4042</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6705</v>
+        <v>-0.2283</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2376</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4329</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3905</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8642</v>
+        <v>-1.103</v>
       </c>
       <c r="E19" t="n">
-        <v>0.584</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4483</v>
+        <v>-1.1754</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0545</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2905</v>
+        <v>0.0518</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8893</v>
+        <v>0.3776</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5987</v>
+        <v>-0.3258</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8837</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BUCETA</t>
+          <t>A. KOVAC MARTINEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5131</v>
+        <v>-2.9549</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.879</v>
+        <v>-0.8885</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6341</v>
+        <v>-2.0664</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3893</v>
+        <v>-3.878</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6622</v>
+        <v>-3.0289</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2729</v>
+        <v>-0.8491</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3236</v>
+        <v>-0.9032</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3236</v>
+        <v>-0.3114</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.5918</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-2.9748</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3385</v>
+        <v>-2.7175</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2729</v>
+        <v>-0.2573</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3681</v>
+        <v>-0.4467</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4446</v>
+        <v>0.0147</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0765</v>
+        <v>-0.4614</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.492</v>
+        <v>0.3905</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.492</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. KOVAC MARTINEZ</t>
+          <t>J. RODRIGUEZ BUCETA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0537</v>
+        <v>-3.1096</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1955</v>
+        <v>-1.2884</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8582</v>
+        <v>-1.8212</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.878</v>
+        <v>-1.3893</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.0289</v>
+        <v>-1.6622</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8491</v>
+        <v>0.2729</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9032</v>
+        <v>-1.3236</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3114</v>
+        <v>-1.3236</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5918</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9748</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.7175</v>
+        <v>-0.3385</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2573</v>
+        <v>0.2729</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5454</v>
+        <v>-0.2283</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2923</v>
+        <v>0.0353</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2531</v>
+        <v>-0.2636</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3905</v>
+        <v>-1.492</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3905</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. BELLO CASTRO</t>
+          <t>R. SANTORUM OTERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0162</v>
+        <v>-4.2002</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.617</v>
+        <v>-2.9722</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3991</v>
+        <v>-1.228</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.9618</v>
+        <v>-4.4265</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5625</v>
+        <v>-2.8044</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3993</v>
+        <v>-1.6222</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0911</v>
+        <v>-2.6016</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1158</v>
+        <v>-1.242</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2069</v>
+        <v>-1.3597</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.0529</v>
+        <v>-1.8249</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.4467</v>
+        <v>-1.5624</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6062</v>
+        <v>-0.2625</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7626</v>
+        <v>0.9792</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1415</v>
+        <v>-0.8681</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2504</v>
+        <v>-0.3705</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1089</v>
+        <v>-0.4976</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1152</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. SANTORUM OTERO</t>
+          <t>M. BELLO CASTRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1569</v>
+        <v>-4.4744</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8698</v>
+        <v>-1.1287</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2871</v>
+        <v>-3.3457</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4265</v>
+        <v>-3.9618</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8044</v>
+        <v>-2.5625</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6222</v>
+        <v>-1.3993</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.6016</v>
+        <v>0.0911</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.242</v>
+        <v>-0.1158</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3597</v>
+        <v>0.2069</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8249</v>
+        <v>-4.0529</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5624</v>
+        <v>-2.4467</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2625</v>
+        <v>-1.6062</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9792</v>
+        <v>1.7626</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8248</v>
+        <v>-0.3167</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2682</v>
+        <v>0.7387</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5566</v>
+        <v>-1.0554</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1152</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7061</v>
+        <v>-5.4747</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.84</v>
+        <v>-1.6353</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8661</v>
+        <v>-3.8394</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2973</v>
@@ -2326,13 +2326,13 @@
         <v>1.7626</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9583</v>
+        <v>-1.7269</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4464</v>
+        <v>-0.2417</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5119</v>
+        <v>-1.4852</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2754</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8602</v>
+        <v>-5.6953</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0859</v>
+        <v>-3.1882</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7743</v>
+        <v>-2.507</v>
       </c>
       <c r="G25" t="n">
         <v>-4.3018</v>
@@ -2404,13 +2404,13 @@
         <v>1.7626</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.517</v>
+        <v>-0.352</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4493</v>
+        <v>0.347</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9663</v>
+        <v>-0.699</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8249</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.4505</v>
+        <v>-6.937</v>
       </c>
       <c r="E26" t="n">
         <v>-4.1574</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.2931</v>
+        <v>-2.7796</v>
       </c>
       <c r="G26" t="n">
         <v>-3.9024</v>
@@ -2482,13 +2482,13 @@
         <v>1.1751</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.2139</v>
+        <v>-1.7004</v>
       </c>
       <c r="T26" t="n">
         <v>-0.387</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.8269</v>
+        <v>-1.3134</v>
       </c>
       <c r="V26" t="n">
         <v>-0.5507</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-26.5599</v>
+        <v>-25.1955</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.579299999999999</v>
+        <v>-1.5794</v>
       </c>
       <c r="F27" t="n">
-        <v>-24.9806</v>
+        <v>-23.616</v>
       </c>
       <c r="G27" t="n">
         <v>-24.5448</v>
@@ -2533,10 +2533,10 @@
         <v>-9.577400000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.295800000000002</v>
+        <v>-2.295800000000003</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.7238000000000003</v>
+        <v>-0.7237999999999997</v>
       </c>
       <c r="L27" t="n">
         <v>-1.5722</v>
@@ -2560,13 +2560,13 @@
         <v>12.7299</v>
       </c>
       <c r="S27" t="n">
-        <v>-9.318999999999999</v>
+        <v>-7.9544</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5204999999999997</v>
+        <v>0.5205</v>
       </c>
       <c r="U27" t="n">
-        <v>-9.839399999999999</v>
+        <v>-8.4749</v>
       </c>
       <c r="V27" t="n">
         <v>3.3869</v>
